--- a/backend/data/data.xlsx
+++ b/backend/data/data.xlsx
@@ -14,84 +14,84 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t>BuildingNumber</t>
+  </si>
   <si>
     <t>BuildingName</t>
   </si>
   <si>
+    <t>FloorNumber</t>
+  </si>
+  <si>
+    <t>FloorDesc</t>
+  </si>
+  <si>
+    <t>RoomNumber</t>
+  </si>
+  <si>
+    <t>SpaceUseCode</t>
+  </si>
+  <si>
+    <t>SpaceUse</t>
+  </si>
+  <si>
+    <t>IsRaiderRoom</t>
+  </si>
+  <si>
+    <t>Campus</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>BuildingLocation</t>
+  </si>
+  <si>
+    <t>BuildingLat</t>
+  </si>
+  <si>
+    <t>BuildingLon</t>
+  </si>
+  <si>
+    <t>RoomID</t>
+  </si>
+  <si>
+    <t>RoomLon</t>
+  </si>
+  <si>
+    <t>RoomLat</t>
+  </si>
+  <si>
+    <t>WifiStatus</t>
+  </si>
+  <si>
     <t>AudioStatus</t>
   </si>
   <si>
-    <t>WifiStatus</t>
-  </si>
-  <si>
-    <t>Latitude</t>
-  </si>
-  <si>
-    <t>Longitude</t>
-  </si>
-  <si>
-    <t>Holden Hall</t>
+    <t>health sciences</t>
+  </si>
+  <si>
+    <t>basement</t>
+  </si>
+  <si>
+    <t>classroom</t>
+  </si>
+  <si>
+    <t>ttu main</t>
+  </si>
+  <si>
+    <t>1312 kentuky</t>
+  </si>
+  <si>
+    <t>main</t>
   </si>
   <si>
     <t>Inactive</t>
   </si>
   <si>
     <t>Active</t>
-  </si>
-  <si>
-    <t>West Hall</t>
-  </si>
-  <si>
-    <t>Admin Building</t>
-  </si>
-  <si>
-    <t>Student Union Building</t>
-  </si>
-  <si>
-    <t>Library</t>
-  </si>
-  <si>
-    <t>Agricultural Pavilion</t>
-  </si>
-  <si>
-    <t>Special Collections Library</t>
-  </si>
-  <si>
-    <t>Food Technology Building</t>
-  </si>
-  <si>
-    <t>Psychology Building</t>
-  </si>
-  <si>
-    <t>Gates Hall</t>
-  </si>
-  <si>
-    <t>Wall Hall</t>
-  </si>
-  <si>
-    <t>Knapp Hall</t>
-  </si>
-  <si>
-    <t>Learning Hall</t>
-  </si>
-  <si>
-    <t>Food Pantry</t>
-  </si>
-  <si>
-    <t>McClellan Hall</t>
-  </si>
-  <si>
-    <t>Sneed Hall</t>
-  </si>
-  <si>
-    <t>Livermore Center</t>
-  </si>
-  <si>
-    <t>Experimental Sciences Building</t>
-  </si>
-  <si>
-    <t>Madoxx Engineering Research Center</t>
   </si>
 </sst>
 </file>
@@ -110,30 +110,50 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFe8e8e8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFc6c6c6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFc6c6c6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFc6c6c6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFc6c6c6"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -147,18 +167,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -469,354 +498,139 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="13.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="8" width="14.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="4">
-        <v>33.5856041036936</v>
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="E2" s="4">
-        <v>-101.873726393183</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="4">
-        <v>33.5853113913359</v>
-      </c>
-      <c r="E3" s="4">
-        <v>-101.872299458104</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="4">
-        <v>33.5833897435391</v>
-      </c>
-      <c r="E4" s="4">
-        <v>-101.874906565217</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4">
-        <v>33.5815462621146</v>
-      </c>
-      <c r="E5" s="4">
-        <v>-101.874863649869</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4">
-        <v>33.5815484966595</v>
-      </c>
-      <c r="E6" s="4">
-        <v>-101.876531983759</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="4">
-        <v>33.5822009818309</v>
-      </c>
-      <c r="E7" s="4">
-        <v>-101.876770700403</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="4">
-        <v>33.5819417759833</v>
-      </c>
-      <c r="E8" s="4">
-        <v>-101.877392972844</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="4">
-        <v>33.5826123814406</v>
-      </c>
-      <c r="E9" s="4">
-        <v>-101.87622985745</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="4">
-        <v>33.5806150920787</v>
-      </c>
-      <c r="E10" s="4">
-        <v>-101.877147483498</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="4">
-        <v>33.5791987035008</v>
-      </c>
-      <c r="E11" s="4">
-        <v>-101.877211277659</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="4">
-        <v>33.5791455552597</v>
-      </c>
-      <c r="E12" s="4">
-        <v>-101.876503163863</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="4">
-        <v>33.5805709417876</v>
-      </c>
-      <c r="E13" s="4">
-        <v>-101.873132424746</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="4">
-        <v>33.5816801515584</v>
-      </c>
-      <c r="E14" s="4">
-        <v>-101.872267571469</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="4">
+        <v>110</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="4">
-        <v>33.5829347106625</v>
-      </c>
-      <c r="E15" s="4">
-        <v>-101.872510337326</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="2" t="s">
+      <c r="H2" s="4">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="4">
-        <v>33.5813609787148</v>
-      </c>
-      <c r="E16" s="4">
-        <v>-101.873189323</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="2" t="s">
+      <c r="J2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="4">
-        <v>33.5852325962025</v>
-      </c>
-      <c r="E17" s="4">
-        <v>-101.871325413139</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="2" t="s">
+      <c r="K2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="4">
-        <v>33.5879248668759</v>
-      </c>
-      <c r="E18" s="4">
-        <v>-101.87608589962</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="2" t="s">
+      <c r="L2" s="6">
+        <v>33.5831379050788</v>
+      </c>
+      <c r="M2" s="6">
+        <v>-101.873049597475</v>
+      </c>
+      <c r="N2" s="4">
+        <v>100111</v>
+      </c>
+      <c r="O2" s="6">
+        <v>-101.873253418947</v>
+      </c>
+      <c r="P2" s="6">
+        <v>33.5832176597843</v>
+      </c>
+      <c r="Q2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="4">
-        <v>33.5857160735429</v>
-      </c>
-      <c r="E19" s="4">
-        <v>-101.877102481552</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
-      <c r="A20" s="2" t="s">
+      <c r="R2" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="4">
-        <v>33.5855264749162</v>
-      </c>
-      <c r="E20" s="4">
-        <v>-101.875293117493</v>
       </c>
     </row>
   </sheetData>
